--- a/data/盗み金策_実測検証テンプレ_除外リスト追加.xlsx
+++ b/data/盗み金策_実測検証テンプレ_除外リスト追加.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuya\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d2570435abe0c053/ドキュメント/GitHub/dq10 tool/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EA080A-6087-4E56-B5E7-6690786DA89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{C9EA080A-6087-4E56-B5E7-6690786DA89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30AA8D5D-BDBC-417A-BD30-AE6C3D8AF79E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="検証ログ" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="160">
   <si>
     <t>検証日</t>
   </si>
@@ -132,12 +132,6 @@
     <t>グレイトドラゴン</t>
   </si>
   <si>
-    <t>迅雷の丘、ドランド平原</t>
-  </si>
-  <si>
-    <t>自まも＋盗賊2＋旅</t>
-  </si>
-  <si>
     <t>大きなこうら</t>
   </si>
   <si>
@@ -148,12 +142,6 @@
   </si>
   <si>
     <t>硬い。10分時点では候補止まり</t>
-  </si>
-  <si>
-    <t>プテラノドン・強</t>
-  </si>
-  <si>
-    <t>ゲルヘナ幻野</t>
   </si>
   <si>
     <t>大きな化石</t>
@@ -225,16 +213,10 @@
     <t>最有力。30分以上の追加検証対象</t>
   </si>
   <si>
-    <t>比較用おすすめ。エモノ呼びあり</t>
-  </si>
-  <si>
     <t>基本構成</t>
   </si>
   <si>
     <t>かなり良い</t>
-  </si>
-  <si>
-    <t>自盗賊＋盗賊2＋旅</t>
   </si>
   <si>
     <t>盗み特化。呼べない敵向け</t>
@@ -477,6 +459,99 @@
   <si>
     <t>てんとうスカラベ</t>
   </si>
+  <si>
+    <t>デスマドモアゼル</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>ごうけつぐま</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>わかめ王子・強</t>
+    <rPh sb="3" eb="5">
+      <t>オウジ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>キョウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>ワニバーン</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>ミーラカンス</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>むくろカサゴ</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>コットンキャンディ</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>にじくじゃく</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>死のさそり</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>神代の遺構｜ムニエカ・隠し通路</t>
+  </si>
+  <si>
+    <t>オルセコ王国領｜バルディア山岳地帯｜ザハディガル岩峰</t>
+  </si>
+  <si>
+    <t>血潮の浜辺｜閉ざされた水路｜ジャリムバハ砂漠</t>
+  </si>
+  <si>
+    <t>オーフィーヌ海底｜ナドラガンドの混沌</t>
+  </si>
+  <si>
+    <t>キュロン湿原</t>
+  </si>
+  <si>
+    <t>歌姫の絶望</t>
+  </si>
+  <si>
+    <t>神具解放の審問宮1｜神具解放の審問宮2｜神具解放の審問宮3</t>
+  </si>
+  <si>
+    <t>古・ティプローネ高地｜現・ティプローネ高地｜輝きの草原</t>
+  </si>
+  <si>
+    <t>試みの荒野｜三闘士の憤怒</t>
+  </si>
+  <si>
+    <t>自まも＋レン2＋盗賊</t>
+    <rPh sb="8" eb="10">
+      <t>トウゾク</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>自まも＋レン＋盗賊2</t>
+    <rPh sb="7" eb="9">
+      <t>トウゾク</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>hjp2900以上モンスター。</t>
+    <rPh sb="7" eb="9">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
 </sst>
 </file>
 
@@ -486,7 +561,7 @@
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="#,##0&quot; G&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -554,6 +629,12 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -611,7 +692,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -652,10 +733,19 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -669,15 +759,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -904,7 +991,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="3" max="3" width="61.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
@@ -1011,17 +1098,17 @@
       </c>
     </row>
     <row r="2" spans="1:30">
-      <c r="A2" s="8">
+      <c r="A2" s="27">
         <v>46193</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>31</v>
+        <v>139</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>148</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="E2" s="8">
         <v>10</v>
@@ -1030,7 +1117,7 @@
         <v>18</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H2" s="8">
         <v>3</v>
@@ -1039,7 +1126,7 @@
         <v>2000</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K2" s="8">
         <v>0</v>
@@ -1101,24 +1188,24 @@
         <v>3</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AD2" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:30">
-      <c r="A3" s="8">
+      <c r="A3" s="27">
         <v>46193</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>38</v>
+      <c r="B3" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>149</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="E3" s="8">
         <v>10</v>
@@ -1127,7 +1214,7 @@
         <v>42</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H3" s="8">
         <v>10</v>
@@ -1136,7 +1223,7 @@
         <v>948</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K3" s="8">
         <v>1</v>
@@ -1198,17 +1285,25 @@
         <v>4</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AD3" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="A4" s="27">
+        <v>46193</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
@@ -1252,10 +1347,18 @@
       <c r="AD4" s="8"/>
     </row>
     <row r="5" spans="1:30">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="A5" s="27">
+        <v>46193</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -1299,10 +1402,18 @@
       <c r="AD5" s="8"/>
     </row>
     <row r="6" spans="1:30">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+      <c r="A6" s="27">
+        <v>46193</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -1346,10 +1457,18 @@
       <c r="AD6" s="8"/>
     </row>
     <row r="7" spans="1:30">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="A7" s="27">
+        <v>46193</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -1393,10 +1512,18 @@
       <c r="AD7" s="8"/>
     </row>
     <row r="8" spans="1:30">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
+      <c r="A8" s="27">
+        <v>46193</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -1440,10 +1567,18 @@
       <c r="AD8" s="8"/>
     </row>
     <row r="9" spans="1:30">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="A9" s="27">
+        <v>46193</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -1487,10 +1622,18 @@
       <c r="AD9" s="8"/>
     </row>
     <row r="10" spans="1:30">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="A10" s="27">
+        <v>46193</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>158</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -13164,11 +13307,11 @@
       <c r="S258" s="8"/>
       <c r="T258" s="8"/>
       <c r="U258" s="9">
-        <f t="shared" ref="U258:U321" si="20">H258*I258+K258*L258+M258*N258+O258*P258+Q258*R258+S258*T258</f>
+        <f t="shared" ref="U258:U301" si="20">H258*I258+K258*L258+M258*N258+O258*P258+Q258*R258+S258*T258</f>
         <v>0</v>
       </c>
       <c r="V258" s="9">
-        <f t="shared" ref="V258:V321" si="21">IF(E258&gt;0,U258/E258*60,0)</f>
+        <f t="shared" ref="V258:V301" si="21">IF(E258&gt;0,U258/E258*60,0)</f>
         <v>0</v>
       </c>
       <c r="W258" s="9">
@@ -15234,8 +15377,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -15293,20 +15437,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19.5">
-      <c r="A1" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="17"/>
+      <c r="A1" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="3" spans="1:15" ht="15">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -15329,36 +15473,36 @@
       <c r="H3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
+      <c r="J3" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
     </row>
     <row r="4" spans="1:15" ht="15">
-      <c r="A4" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
       <c r="J4" s="10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K4" s="11">
         <f>COUNTA(検証ログ!B2:B301)</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L4" s="10"/>
       <c r="M4" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N4" s="12">
         <f>MAX(検証ログ!V2:V301)</f>
@@ -15376,7 +15520,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="J5" s="10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K5" s="11">
         <f>SUM(検証ログ!E2:E301)</f>
@@ -15384,7 +15528,7 @@
       </c>
       <c r="L5" s="10"/>
       <c r="M5" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N5" s="12">
         <f>IFERROR(AVERAGEIF(検証ログ!V2:V301,"&gt;0"),0)</f>
@@ -15394,7 +15538,7 @@
     </row>
     <row r="6" spans="1:15" ht="15">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
@@ -15418,7 +15562,7 @@
         <v>29</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K6" s="11">
         <f>SUM(検証ログ!H2:H301)</f>
@@ -15426,7 +15570,7 @@
       </c>
       <c r="L6" s="10"/>
       <c r="M6" s="10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N6" s="12">
         <f>SUM(検証ログ!K2:K301)</f>
@@ -15446,7 +15590,7 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="J7" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K7" s="11">
         <f>SUM(検証ログ!M2:M301)+SUM(検証ログ!O2:O301)+SUM(検証ログ!Q2:Q301)+SUM(検証ログ!S2:S301)</f>
@@ -16587,28 +16731,28 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15">
       <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -16616,22 +16760,22 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
+        <v>57</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>157</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -16639,19 +16783,19 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>158</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -16659,16 +16803,16 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -16679,16 +16823,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -16699,16 +16843,16 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -16719,10 +16863,10 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -16742,20 +16886,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="A1" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -16767,10 +16911,10 @@
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -16781,10 +16925,10 @@
     </row>
     <row r="5" spans="1:8" ht="29.25">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -16795,10 +16939,10 @@
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -16809,10 +16953,10 @@
     </row>
     <row r="7" spans="1:8" ht="29.25">
       <c r="A7" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -16823,10 +16967,10 @@
     </row>
     <row r="8" spans="1:8" ht="29.25">
       <c r="A8" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -16837,10 +16981,10 @@
     </row>
     <row r="9" spans="1:8" ht="29.25">
       <c r="A9" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -16851,10 +16995,10 @@
     </row>
     <row r="10" spans="1:8" ht="15">
       <c r="A10" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -16875,10 +17019,10 @@
     </row>
     <row r="12" spans="1:8" ht="32.1" customHeight="1">
       <c r="A12" s="15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -16889,26 +17033,26 @@
     </row>
     <row r="13" spans="1:8" ht="32.1" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="32.1" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="32.1" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -16935,50 +17079,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="A1" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="36" customHeight="1">
-      <c r="A2" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="A2" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H4" s="14" t="s">
         <v>29</v>
@@ -16986,600 +17130,600 @@
     </row>
     <row r="5" spans="1:8" ht="28.5">
       <c r="A5" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28.5">
       <c r="A6" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17.25">
+      <c r="A8" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.25">
+      <c r="A9" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="17.25">
+      <c r="A10" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="17.25">
+      <c r="A11" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17.25">
+      <c r="A12" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B12" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17.25">
+      <c r="A13" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="B13" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="17.25">
+      <c r="A14" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="17.25">
-      <c r="A8" s="25" t="s">
+      <c r="B14" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17.25">
+      <c r="A15" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17.25">
+      <c r="A16" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17.25">
+      <c r="A17" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17.25">
+      <c r="A18" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="17.25">
+      <c r="A19" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="17.25">
+      <c r="A20" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="28.5">
+      <c r="A21" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.25">
+      <c r="A22" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="17.25">
+      <c r="A23" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.25">
+      <c r="A24" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="17.25">
+      <c r="A25" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="28.5">
+      <c r="A26" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="17.25">
+      <c r="A27" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="17.25">
-      <c r="A9" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="17.25">
-      <c r="A10" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="17.25">
-      <c r="A11" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="17.25">
-      <c r="A12" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="17.25">
-      <c r="A13" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="17.25">
-      <c r="A14" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="17.25">
-      <c r="A15" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="17.25">
-      <c r="A16" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="17.25">
-      <c r="A17" s="25" t="s">
+      <c r="B27" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="17.25">
-      <c r="A18" s="25" t="s">
+      <c r="C27" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="17.25">
-      <c r="A19" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="17.25">
-      <c r="A20" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="28.5">
-      <c r="A21" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="17.25">
-      <c r="A22" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="17.25">
-      <c r="A23" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="17.25">
-      <c r="A24" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="17.25">
-      <c r="A25" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="28.5">
-      <c r="A26" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="17.25">
-      <c r="A27" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="D27" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:8">

--- a/data/盗み金策_実測検証テンプレ_除外リスト追加.xlsx
+++ b/data/盗み金策_実測検証テンプレ_除外リスト追加.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d2570435abe0c053/ドキュメント/GitHub/dq10 tool/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{C9EA080A-6087-4E56-B5E7-6690786DA89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30AA8D5D-BDBC-417A-BD30-AE6C3D8AF79E}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{C9EA080A-6087-4E56-B5E7-6690786DA89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F07BAD01-4AAE-4185-9026-A2922930B989}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28890" yWindow="0" windowWidth="13605" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="検証ログ" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="157">
   <si>
     <t>検証日</t>
   </si>
@@ -132,16 +132,7 @@
     <t>グレイトドラゴン</t>
   </si>
   <si>
-    <t>大きなこうら</t>
-  </si>
-  <si>
-    <t>烈風石</t>
-  </si>
-  <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>硬い。10分時点では候補止まり</t>
   </si>
   <si>
     <t>大きな化石</t>
@@ -460,10 +451,6 @@
     <t>てんとうスカラベ</t>
   </si>
   <si>
-    <t>デスマドモアゼル</t>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
     <t>ごうけつぐま</t>
     <phoneticPr fontId="10"/>
   </si>
@@ -505,12 +492,6 @@
     <phoneticPr fontId="10"/>
   </si>
   <si>
-    <t>神代の遺構｜ムニエカ・隠し通路</t>
-  </si>
-  <si>
-    <t>オルセコ王国領｜バルディア山岳地帯｜ザハディガル岩峰</t>
-  </si>
-  <si>
     <t>血潮の浜辺｜閉ざされた水路｜ジャリムバハ砂漠</t>
   </si>
   <si>
@@ -549,6 +530,27 @@
     <t>hjp2900以上モンスター。</t>
     <rPh sb="7" eb="9">
       <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>batu</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>ふしぎな海草</t>
+    <rPh sb="4" eb="6">
+      <t>カイソウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人魚の涙</t>
+    <rPh sb="0" eb="2">
+      <t>ニンギョ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナミダ</t>
     </rPh>
     <phoneticPr fontId="10"/>
   </si>
@@ -692,7 +694,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -765,6 +767,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -784,7 +789,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ValidationLog" displayName="ValidationLog" ref="A1:AD301">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ValidationLog" displayName="ValidationLog" ref="A1:AD300">
   <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="検証日"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="モンスター名"/>
@@ -986,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD301"/>
+  <dimension ref="A1:AD300"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1101,38 +1106,38 @@
       <c r="A2" s="27">
         <v>46193</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>148</v>
+      <c r="B2" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>154</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E2" s="8">
+        <v>15</v>
+      </c>
+      <c r="F2" s="8">
+        <v>42</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="8">
         <v>10</v>
       </c>
-      <c r="F2" s="8">
-        <v>18</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="8">
-        <v>3</v>
-      </c>
       <c r="I2" s="8">
-        <v>2000</v>
+        <v>948</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="8">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="M2" s="8">
         <v>0</v>
@@ -1147,7 +1152,7 @@
         <v>19000</v>
       </c>
       <c r="Q2" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" s="8">
         <v>4875</v>
@@ -1159,152 +1164,124 @@
         <v>1000</v>
       </c>
       <c r="U2" s="9">
-        <f t="shared" ref="U2:U65" si="0">H2*I2+K2*L2+M2*N2+O2*P2+Q2*R2+S2*T2</f>
-        <v>10875</v>
+        <f t="shared" ref="U2:U64" si="0">H2*I2+K2*L2+M2*N2+O2*P2+Q2*R2+S2*T2</f>
+        <v>33230</v>
       </c>
       <c r="V2" s="9">
-        <f t="shared" ref="V2:V65" si="1">IF(E2&gt;0,U2/E2*60,0)</f>
-        <v>65250</v>
+        <f t="shared" ref="V2:V64" si="1">IF(E2&gt;0,U2/E2*60,0)</f>
+        <v>132920</v>
       </c>
       <c r="W2" s="9">
-        <f t="shared" ref="W2:W65" si="2">IF(E2&gt;0,F2/E2*60,0)</f>
-        <v>108</v>
+        <f t="shared" ref="W2:W64" si="2">IF(E2&gt;0,F2/E2*60,0)</f>
+        <v>168</v>
       </c>
       <c r="X2" s="9">
-        <f t="shared" ref="X2:X65" si="3">IF(E2&gt;0,H2/E2*60,0)</f>
-        <v>18</v>
+        <f t="shared" ref="X2:X64" si="3">IF(E2&gt;0,H2/E2*60,0)</f>
+        <v>40</v>
       </c>
       <c r="Y2" s="9">
-        <f t="shared" ref="Y2:Y65" si="4">IF(E2&gt;0,K2/E2*60,0)</f>
-        <v>0</v>
+        <f t="shared" ref="Y2:Y64" si="4">IF(E2&gt;0,K2/E2*60,0)</f>
+        <v>4</v>
       </c>
       <c r="Z2" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA2" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB2" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AD2" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:30">
       <c r="A3" s="27">
         <v>46193</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>140</v>
+      <c r="B3" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E3" s="8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3" s="8">
-        <v>42</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>35</v>
+        <v>100</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="H3" s="8">
-        <v>10</v>
-      </c>
-      <c r="I3" s="8">
-        <v>948</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I3" s="8"/>
       <c r="J3" s="8" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="K3" s="8">
-        <v>1</v>
-      </c>
-      <c r="L3" s="8">
-        <v>14000</v>
-      </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
-      <c r="N3" s="8">
-        <v>99000</v>
-      </c>
-      <c r="O3" s="8">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <v>19000</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>2</v>
-      </c>
-      <c r="R3" s="8">
-        <v>4875</v>
-      </c>
-      <c r="S3" s="8">
-        <v>0</v>
-      </c>
-      <c r="T3" s="8">
-        <v>1000</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
       <c r="U3" s="9">
         <f t="shared" si="0"/>
-        <v>33230</v>
+        <v>0</v>
       </c>
       <c r="V3" s="9">
         <f t="shared" si="1"/>
-        <v>199380</v>
+        <v>0</v>
       </c>
       <c r="W3" s="9">
         <f t="shared" si="2"/>
-        <v>252</v>
+        <v>400</v>
       </c>
       <c r="X3" s="9">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="Y3" s="9">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="Z3" s="8">
-        <v>4</v>
-      </c>
-      <c r="AA3" s="8">
-        <v>4</v>
-      </c>
-      <c r="AB3" s="8">
-        <v>4</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD3" s="8" t="s">
-        <v>38</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="8"/>
     </row>
     <row r="4" spans="1:30">
       <c r="A4" s="27">
         <v>46193</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="E4" s="8">
+        <v>15</v>
+      </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
@@ -1351,15 +1328,17 @@
         <v>46193</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C5" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="8">
+        <v>15</v>
+      </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -1406,15 +1385,17 @@
         <v>46193</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="8"/>
+        <v>151</v>
+      </c>
+      <c r="E6" s="8">
+        <v>15</v>
+      </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
@@ -1461,15 +1442,17 @@
         <v>46193</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="E7" s="8">
+        <v>15</v>
+      </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
@@ -1516,15 +1499,17 @@
         <v>46193</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E8" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="E8" s="8">
+        <v>15</v>
+      </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
@@ -1571,15 +1556,17 @@
         <v>46193</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9" s="8"/>
+        <v>152</v>
+      </c>
+      <c r="E9" s="8">
+        <v>15</v>
+      </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -1622,18 +1609,10 @@
       <c r="AD9" s="8"/>
     </row>
     <row r="10" spans="1:30">
-      <c r="A10" s="27">
-        <v>46193</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>158</v>
-      </c>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -4236,23 +4215,23 @@
       <c r="S65" s="8"/>
       <c r="T65" s="8"/>
       <c r="U65" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="U65:U128" si="5">H65*I65+K65*L65+M65*N65+O65*P65+Q65*R65+S65*T65</f>
         <v>0</v>
       </c>
       <c r="V65" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="V65:V128" si="6">IF(E65&gt;0,U65/E65*60,0)</f>
         <v>0</v>
       </c>
       <c r="W65" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="W65:W128" si="7">IF(E65&gt;0,F65/E65*60,0)</f>
         <v>0</v>
       </c>
       <c r="X65" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="X65:X128" si="8">IF(E65&gt;0,H65/E65*60,0)</f>
         <v>0</v>
       </c>
       <c r="Y65" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="Y65:Y128" si="9">IF(E65&gt;0,K65/E65*60,0)</f>
         <v>0</v>
       </c>
       <c r="Z65" s="8"/>
@@ -4283,23 +4262,23 @@
       <c r="S66" s="8"/>
       <c r="T66" s="8"/>
       <c r="U66" s="9">
-        <f t="shared" ref="U66:U129" si="5">H66*I66+K66*L66+M66*N66+O66*P66+Q66*R66+S66*T66</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V66" s="9">
-        <f t="shared" ref="V66:V129" si="6">IF(E66&gt;0,U66/E66*60,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W66" s="9">
-        <f t="shared" ref="W66:W129" si="7">IF(E66&gt;0,F66/E66*60,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X66" s="9">
-        <f t="shared" ref="X66:X129" si="8">IF(E66&gt;0,H66/E66*60,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y66" s="9">
-        <f t="shared" ref="Y66:Y129" si="9">IF(E66&gt;0,K66/E66*60,0)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z66" s="8"/>
@@ -7244,23 +7223,23 @@
       <c r="S129" s="8"/>
       <c r="T129" s="8"/>
       <c r="U129" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="U129:U192" si="10">H129*I129+K129*L129+M129*N129+O129*P129+Q129*R129+S129*T129</f>
         <v>0</v>
       </c>
       <c r="V129" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="V129:V192" si="11">IF(E129&gt;0,U129/E129*60,0)</f>
         <v>0</v>
       </c>
       <c r="W129" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="W129:W192" si="12">IF(E129&gt;0,F129/E129*60,0)</f>
         <v>0</v>
       </c>
       <c r="X129" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="X129:X192" si="13">IF(E129&gt;0,H129/E129*60,0)</f>
         <v>0</v>
       </c>
       <c r="Y129" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="Y129:Y192" si="14">IF(E129&gt;0,K129/E129*60,0)</f>
         <v>0</v>
       </c>
       <c r="Z129" s="8"/>
@@ -7291,23 +7270,23 @@
       <c r="S130" s="8"/>
       <c r="T130" s="8"/>
       <c r="U130" s="9">
-        <f t="shared" ref="U130:U193" si="10">H130*I130+K130*L130+M130*N130+O130*P130+Q130*R130+S130*T130</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="V130" s="9">
-        <f t="shared" ref="V130:V193" si="11">IF(E130&gt;0,U130/E130*60,0)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="W130" s="9">
-        <f t="shared" ref="W130:W193" si="12">IF(E130&gt;0,F130/E130*60,0)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="X130" s="9">
-        <f t="shared" ref="X130:X193" si="13">IF(E130&gt;0,H130/E130*60,0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Y130" s="9">
-        <f t="shared" ref="Y130:Y193" si="14">IF(E130&gt;0,K130/E130*60,0)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z130" s="8"/>
@@ -10252,23 +10231,23 @@
       <c r="S193" s="8"/>
       <c r="T193" s="8"/>
       <c r="U193" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="U193:U256" si="15">H193*I193+K193*L193+M193*N193+O193*P193+Q193*R193+S193*T193</f>
         <v>0</v>
       </c>
       <c r="V193" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="V193:V256" si="16">IF(E193&gt;0,U193/E193*60,0)</f>
         <v>0</v>
       </c>
       <c r="W193" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="W193:W256" si="17">IF(E193&gt;0,F193/E193*60,0)</f>
         <v>0</v>
       </c>
       <c r="X193" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="X193:X256" si="18">IF(E193&gt;0,H193/E193*60,0)</f>
         <v>0</v>
       </c>
       <c r="Y193" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="Y193:Y256" si="19">IF(E193&gt;0,K193/E193*60,0)</f>
         <v>0</v>
       </c>
       <c r="Z193" s="8"/>
@@ -10299,23 +10278,23 @@
       <c r="S194" s="8"/>
       <c r="T194" s="8"/>
       <c r="U194" s="9">
-        <f t="shared" ref="U194:U257" si="15">H194*I194+K194*L194+M194*N194+O194*P194+Q194*R194+S194*T194</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="V194" s="9">
-        <f t="shared" ref="V194:V257" si="16">IF(E194&gt;0,U194/E194*60,0)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="W194" s="9">
-        <f t="shared" ref="W194:W257" si="17">IF(E194&gt;0,F194/E194*60,0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X194" s="9">
-        <f t="shared" ref="X194:X257" si="18">IF(E194&gt;0,H194/E194*60,0)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Y194" s="9">
-        <f t="shared" ref="Y194:Y257" si="19">IF(E194&gt;0,K194/E194*60,0)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="Z194" s="8"/>
@@ -13260,23 +13239,23 @@
       <c r="S257" s="8"/>
       <c r="T257" s="8"/>
       <c r="U257" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="U257:U300" si="20">H257*I257+K257*L257+M257*N257+O257*P257+Q257*R257+S257*T257</f>
         <v>0</v>
       </c>
       <c r="V257" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="V257:V300" si="21">IF(E257&gt;0,U257/E257*60,0)</f>
         <v>0</v>
       </c>
       <c r="W257" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="W257:W300" si="22">IF(E257&gt;0,F257/E257*60,0)</f>
         <v>0</v>
       </c>
       <c r="X257" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="X257:X300" si="23">IF(E257&gt;0,H257/E257*60,0)</f>
         <v>0</v>
       </c>
       <c r="Y257" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="Y257:Y300" si="24">IF(E257&gt;0,K257/E257*60,0)</f>
         <v>0</v>
       </c>
       <c r="Z257" s="8"/>
@@ -13307,23 +13286,23 @@
       <c r="S258" s="8"/>
       <c r="T258" s="8"/>
       <c r="U258" s="9">
-        <f t="shared" ref="U258:U301" si="20">H258*I258+K258*L258+M258*N258+O258*P258+Q258*R258+S258*T258</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V258" s="9">
-        <f t="shared" ref="V258:V301" si="21">IF(E258&gt;0,U258/E258*60,0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W258" s="9">
-        <f t="shared" ref="W258:W301" si="22">IF(E258&gt;0,F258/E258*60,0)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="X258" s="9">
-        <f t="shared" ref="X258:X301" si="23">IF(E258&gt;0,H258/E258*60,0)</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="Y258" s="9">
-        <f t="shared" ref="Y258:Y301" si="24">IF(E258&gt;0,K258/E258*60,0)</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z258" s="8"/>
@@ -15306,64 +15285,17 @@
       <c r="AC300" s="8"/>
       <c r="AD300" s="8"/>
     </row>
-    <row r="301" spans="1:30">
-      <c r="A301" s="8"/>
-      <c r="B301" s="8"/>
-      <c r="C301" s="8"/>
-      <c r="D301" s="8"/>
-      <c r="E301" s="8"/>
-      <c r="F301" s="8"/>
-      <c r="G301" s="8"/>
-      <c r="H301" s="8"/>
-      <c r="I301" s="8"/>
-      <c r="J301" s="8"/>
-      <c r="K301" s="8"/>
-      <c r="L301" s="8"/>
-      <c r="M301" s="8"/>
-      <c r="N301" s="8"/>
-      <c r="O301" s="8"/>
-      <c r="P301" s="8"/>
-      <c r="Q301" s="8"/>
-      <c r="R301" s="8"/>
-      <c r="S301" s="8"/>
-      <c r="T301" s="8"/>
-      <c r="U301" s="9">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="V301" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="W301" s="9">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="X301" s="9">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="Y301" s="9">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="Z301" s="8"/>
-      <c r="AA301" s="8"/>
-      <c r="AB301" s="8"/>
-      <c r="AC301" s="8"/>
-      <c r="AD301" s="8"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="10"/>
-  <conditionalFormatting sqref="V2:V301">
-    <cfRule type="dataBar" priority="1">
+  <conditionalFormatting sqref="V2:V300">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
         <color rgb="FF15803D"/>
       </dataBar>
     </cfRule>
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15393,7 +15325,7 @@
               <x14:axisColor auto="1"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>V2:V301</xm:sqref>
+          <xm:sqref>V2:V300</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -15403,19 +15335,19 @@
           <x14:formula1>
             <xm:f>設定!$F$2:$F$6</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D301</xm:sqref>
+          <xm:sqref>D2:D300</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>設定!$J$2:$J$6</xm:f>
           </x14:formula1>
-          <xm:sqref>Z2:AB301</xm:sqref>
+          <xm:sqref>Z2:AB300</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>設定!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>AC2:AC301</xm:sqref>
+          <xm:sqref>AC2:AC300</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -15438,7 +15370,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="19.5">
       <c r="A1" s="20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -15450,7 +15382,7 @@
     </row>
     <row r="3" spans="1:15" ht="15">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -15474,7 +15406,7 @@
         <v>28</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K3" s="18"/>
       <c r="L3" s="18"/>
@@ -15484,7 +15416,7 @@
     </row>
     <row r="4" spans="1:15" ht="15">
       <c r="A4" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -15494,19 +15426,19 @@
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
       <c r="J4" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K4" s="11">
-        <f>COUNTA(検証ログ!B2:B301)</f>
-        <v>9</v>
+        <f>COUNTA(検証ログ!B2:B300)</f>
+        <v>8</v>
       </c>
       <c r="L4" s="10"/>
       <c r="M4" s="10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N4" s="12">
-        <f>MAX(検証ログ!V2:V301)</f>
-        <v>199380</v>
+        <f>MAX(検証ログ!V2:V300)</f>
+        <v>132920</v>
       </c>
       <c r="O4" s="10"/>
     </row>
@@ -15520,25 +15452,25 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="J5" s="10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K5" s="11">
-        <f>SUM(検証ログ!E2:E301)</f>
-        <v>20</v>
+        <f>SUM(検証ログ!E2:E300)</f>
+        <v>120</v>
       </c>
       <c r="L5" s="10"/>
       <c r="M5" s="10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N5" s="12">
-        <f>IFERROR(AVERAGEIF(検証ログ!V2:V301,"&gt;0"),0)</f>
-        <v>132315</v>
+        <f>IFERROR(AVERAGEIF(検証ログ!V2:V300,"&gt;0"),0)</f>
+        <v>132920</v>
       </c>
       <c r="O5" s="10"/>
     </row>
     <row r="6" spans="1:15" ht="15">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
@@ -15562,19 +15494,19 @@
         <v>29</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K6" s="11">
-        <f>SUM(検証ログ!H2:H301)</f>
-        <v>13</v>
+        <f>SUM(検証ログ!H2:H300)</f>
+        <v>38</v>
       </c>
       <c r="L6" s="10"/>
       <c r="M6" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N6" s="12">
-        <f>SUM(検証ログ!K2:K301)</f>
-        <v>1</v>
+        <f>SUM(検証ログ!K2:K300)</f>
+        <v>6</v>
       </c>
       <c r="O6" s="10"/>
     </row>
@@ -15590,19 +15522,19 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="J7" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K7" s="11">
-        <f>SUM(検証ログ!M2:M301)+SUM(検証ログ!O2:O301)+SUM(検証ログ!Q2:Q301)+SUM(検証ログ!S2:S301)</f>
-        <v>3</v>
+        <f>SUM(検証ログ!M2:M300)+SUM(検証ログ!O2:O300)+SUM(検証ログ!Q2:Q300)+SUM(検証ログ!S2:S300)</f>
+        <v>2</v>
       </c>
       <c r="L7" s="10"/>
       <c r="M7" s="10" t="s">
         <v>20</v>
       </c>
       <c r="N7" s="12">
-        <f>SUM(検証ログ!U2:U301)</f>
-        <v>44105</v>
+        <f>SUM(検証ログ!U2:U300)</f>
+        <v>33230</v>
       </c>
       <c r="O7" s="10"/>
     </row>
@@ -16731,28 +16663,28 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -16760,19 +16692,19 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J2">
         <v>2</v>
@@ -16783,16 +16715,16 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -16803,16 +16735,16 @@
         <v>28</v>
       </c>
       <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" t="s">
         <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" t="s">
-        <v>64</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -16823,16 +16755,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -16843,16 +16775,16 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" t="s">
         <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" t="s">
-        <v>71</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -16863,10 +16795,10 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -16887,7 +16819,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20.25">
       <c r="A1" s="25" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -16899,7 +16831,7 @@
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -16911,10 +16843,10 @@
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -16925,10 +16857,10 @@
     </row>
     <row r="5" spans="1:8" ht="29.25">
       <c r="A5" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -16939,10 +16871,10 @@
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -16953,10 +16885,10 @@
     </row>
     <row r="7" spans="1:8" ht="29.25">
       <c r="A7" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -16967,10 +16899,10 @@
     </row>
     <row r="8" spans="1:8" ht="29.25">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -16981,10 +16913,10 @@
     </row>
     <row r="9" spans="1:8" ht="29.25">
       <c r="A9" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -16995,10 +16927,10 @@
     </row>
     <row r="10" spans="1:8" ht="15">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -17019,10 +16951,10 @@
     </row>
     <row r="12" spans="1:8" ht="32.1" customHeight="1">
       <c r="A12" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -17033,26 +16965,26 @@
     </row>
     <row r="13" spans="1:8" ht="32.1" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="32.1" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="32.1" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -17080,7 +17012,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -17092,7 +17024,7 @@
     </row>
     <row r="2" spans="1:8" ht="36" customHeight="1">
       <c r="A2" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -17107,22 +17039,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="F4" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="G4" s="14" t="s">
         <v>102</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="H4" s="14" t="s">
         <v>29</v>
@@ -17130,106 +17062,106 @@
     </row>
     <row r="5" spans="1:8" ht="28.5">
       <c r="A5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28.5">
       <c r="A6" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25">
       <c r="A8" s="16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17.25">
@@ -17237,493 +17169,493 @@
         <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17.25">
       <c r="A10" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.25">
       <c r="A11" s="16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.25">
       <c r="A12" s="16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17.25">
       <c r="A13" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17.25">
       <c r="A14" s="16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17.25">
       <c r="A15" s="16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="17.25">
       <c r="A16" s="16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.25">
       <c r="A17" s="16" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="17.25">
       <c r="A18" s="16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="17.25">
       <c r="A19" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.25">
       <c r="A20" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="C20" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="28.5">
       <c r="A21" s="16" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.25">
       <c r="A22" s="16" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="17.25">
       <c r="A23" s="16" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="17.25">
       <c r="A24" s="16" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="17.25">
       <c r="A25" s="16" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.5">
       <c r="A26" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="H26" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.25">
       <c r="A27" s="16" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:8">
